--- a/artfynd/A 63534-2023 artfynd.xlsx
+++ b/artfynd/A 63534-2023 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>509526</v>
       </c>
       <c r="R3" t="n">
-        <v>6997421</v>
+        <v>6997422</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 63534-2023 artfynd.xlsx
+++ b/artfynd/A 63534-2023 artfynd.xlsx
@@ -815,7 +815,7 @@
         <v>509526</v>
       </c>
       <c r="R3" t="n">
-        <v>6997422</v>
+        <v>6997421</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 63534-2023 artfynd.xlsx
+++ b/artfynd/A 63534-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134967730</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134970817</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134964480</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134960378</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134964275</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,8 +1289,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134971456</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 63534-2023 artfynd.xlsx
+++ b/artfynd/A 63534-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>134967730</v>
       </c>
       <c r="B2" t="n">
-        <v>79130</v>
+        <v>79168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>134970817</v>
       </c>
       <c r="B3" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>134964480</v>
       </c>
       <c r="B4" t="n">
-        <v>58839</v>
+        <v>58844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>134960378</v>
       </c>
       <c r="B5" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>134964275</v>
       </c>
       <c r="B6" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>134971456</v>
       </c>
       <c r="B7" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
